--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>en-us/healthcare-professionals.report.json</t>
+  </si>
+  <si>
+    <t>["hero-menu","cards-nav"]</t>
+  </si>
+  <si>
+    <t>en-us/healthcare-professionals</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>healthcare-professionals</t>
+  </si>
+  <si>
+    <t>2026-08-20T19:06:52.806Z</t>
+  </si>
+  <si>
+    <t>Healthcare Professionals | Medtronic</t>
+  </si>
+  <si>
+    <t>https://www.medtronic.com/en-us/healthcare-professionals.html</t>
+  </si>
+  <si>
     <t>en-us/index.report.json</t>
   </si>
   <si>
@@ -46,19 +70,118 @@
     <t>en-us/index</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-20T13:00:12.206Z</t>
+    <t>2026-09-18T08:06:19.316Z</t>
   </si>
   <si>
     <t>Health tech for the digital age | Medtronic</t>
   </si>
   <si>
     <t>https://www.medtronic.com/en-us/index.html</t>
+  </si>
+  <si>
+    <t>en-us/our-company.report.json</t>
+  </si>
+  <si>
+    <t>["hero-stats","columns-promo-card","columns-promo-card","cards-topic","cards-tiles","cards-articles"]</t>
+  </si>
+  <si>
+    <t>en-us/our-company</t>
+  </si>
+  <si>
+    <t>our-company</t>
+  </si>
+  <si>
+    <t>2026-08-20T15:45:07.736Z</t>
+  </si>
+  <si>
+    <t>Where Health Meets High Tech | Medtronic</t>
+  </si>
+  <si>
+    <t>https://www.medtronic.com/en-us/our-company.html</t>
+  </si>
+  <si>
+    <t>en-us/our-impact.report.json</t>
+  </si>
+  <si>
+    <t>["hero-impact","columns-promo-card","columns-promo-card","cards-topic","cards-tiles","cards-articles"]</t>
+  </si>
+  <si>
+    <t>en-us/our-impact</t>
+  </si>
+  <si>
+    <t>our-impact</t>
+  </si>
+  <si>
+    <t>2026-08-20T19:06:26.376Z</t>
+  </si>
+  <si>
+    <t>A healthy life. A healthy planet. For everyone. | Medtronic</t>
+  </si>
+  <si>
+    <t>https://www.medtronic.com/en-us/our-impact.html</t>
+  </si>
+  <si>
+    <t>en-us/healthcare-professionals/specialties.report.json</t>
+  </si>
+  <si>
+    <t>en-us/healthcare-professionals/specialties</t>
+  </si>
+  <si>
+    <t>specialties</t>
+  </si>
+  <si>
+    <t>2026-08-20T19:07:02.443Z</t>
+  </si>
+  <si>
+    <t>Specialties for Healthcare Professionals | Medtronic</t>
+  </si>
+  <si>
+    <t>https://www.medtronic.com/en-us/healthcare-professionals/specialties.html</t>
+  </si>
+  <si>
+    <t>en-us/our-impact/impact-reporting.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-stats","cards-awards","columns-promo-card","accordion-links","cards-articles"]</t>
+  </si>
+  <si>
+    <t>en-us/our-impact/impact-reporting</t>
+  </si>
+  <si>
+    <t>impact-reporting</t>
+  </si>
+  <si>
+    <t>2026-08-20T19:06:35.472Z</t>
+  </si>
+  <si>
+    <t>Leading with purpose | Medtronic</t>
+  </si>
+  <si>
+    <t>https://www.medtronic.com/en-us/our-impact/impact-reporting.html</t>
+  </si>
+  <si>
+    <t>en-us/healthcare-professionals/specialties/acute-care-monitoring.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-video","cards-product","cards-feature","cards-feature","cards-logos","columns-connect"]</t>
+  </si>
+  <si>
+    <t>en-us/healthcare-professionals/specialties/acute-care-monitoring</t>
+  </si>
+  <si>
+    <t>specialty-detail</t>
+  </si>
+  <si>
+    <t>2026-08-20T19:10:22.423Z</t>
+  </si>
+  <si>
+    <t>Acute Care &amp; Monitoring Solutions | Medtronic</t>
+  </si>
+  <si>
+    <t>https://www.medtronic.com/en-us/healthcare-professionals/specialties/acute-care-monitoring.html</t>
   </si>
 </sst>
 </file>
@@ -447,16 +570,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="44" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
+    <col min="5" max="6" width="26" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +628,162 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -64,7 +64,7 @@
     <t>en-us/index.report.json</t>
   </si>
   <si>
-    <t>["hero-video","hero-video","carousel-news","carousel-news","columns-stats","columns-cta","columns-impact","columns-impact","cards-stats","cards-stats","cards-stats","columns-promo","columns-promo","columns-promo","columns-promo"]</t>
+    <t>["hero-video","hero-video","carousel-news","carousel-news","stats-band","cta-band","impact-band","impact-band","cards-stats","cards-stats","cards-stats","promo-band","promo-band","promo-band","promo-band"]</t>
   </si>
   <si>
     <t>en-us/index</t>
@@ -73,7 +73,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-18T08:06:19.316Z</t>
+    <t>2026-09-18T09:37:51.429Z</t>
   </si>
   <si>
     <t>Health tech for the digital age | Medtronic</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -64,7 +64,7 @@
     <t>en-us/index.report.json</t>
   </si>
   <si>
-    <t>["hero-video","hero-video","carousel-news","carousel-news","stats-band","cta-band","impact-band","impact-band","cards-stats","cards-stats","cards-stats","promo-band","promo-band","promo-band","promo-band"]</t>
+    <t>["hero-video","hero-video","banner-patients","banner-patients","carousel-news","carousel-news","stats-band","cta-band","impact-band","impact-band","cards-stats","cards-stats","cards-stats","promo-band","promo-band","promo-band","promo-band"]</t>
   </si>
   <si>
     <t>en-us/index</t>
@@ -73,7 +73,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-18T09:37:51.429Z</t>
+    <t>2026-09-18T10:31:19.331Z</t>
   </si>
   <si>
     <t>Health tech for the digital age | Medtronic</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -73,7 +73,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-18T10:31:19.331Z</t>
+    <t>2026-09-18T11:02:20.232Z</t>
   </si>
   <si>
     <t>Health tech for the digital age | Medtronic</t>
